--- a/4.质量管理/2.运行记录类文件/TXHS-04-20-2025年度质量指标完成情况.xlsx
+++ b/4.质量管理/2.运行记录类文件/TXHS-04-20-2025年度质量指标完成情况.xlsx
@@ -1002,7 +1002,7 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="83">
+  <cellStyleXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection/>
@@ -1036,6 +1036,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment/>
     </xf>
@@ -1252,7 +1257,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="69">
+  <cellStyles count="74">
     <cellStyle name="Normal" xfId="0"/>
     <cellStyle name="Percent" xfId="15"/>
     <cellStyle name="Currency" xfId="16"/>
@@ -1269,59 +1274,64 @@
     <cellStyle name="Currency [0]" xfId="27"/>
     <cellStyle name="Comma" xfId="28"/>
     <cellStyle name="Comma [0]" xfId="29"/>
-    <cellStyle name="千位分隔" xfId="30"/>
-    <cellStyle name="货币" xfId="31"/>
-    <cellStyle name="百分比" xfId="32"/>
-    <cellStyle name="千位分隔[0]" xfId="33"/>
-    <cellStyle name="货币[0]" xfId="34"/>
-    <cellStyle name="超链接" xfId="35"/>
-    <cellStyle name="已访问的超链接" xfId="36"/>
-    <cellStyle name="注释" xfId="37"/>
-    <cellStyle name="警告文本" xfId="38"/>
-    <cellStyle name="标题" xfId="39"/>
-    <cellStyle name="解释性文本" xfId="40"/>
-    <cellStyle name="标题 1" xfId="41"/>
-    <cellStyle name="标题 2" xfId="42"/>
-    <cellStyle name="标题 3" xfId="43"/>
-    <cellStyle name="标题 4" xfId="44"/>
-    <cellStyle name="输入" xfId="45"/>
-    <cellStyle name="输出" xfId="46"/>
-    <cellStyle name="计算" xfId="47"/>
-    <cellStyle name="检查单元格" xfId="48"/>
-    <cellStyle name="链接单元格" xfId="49"/>
-    <cellStyle name="汇总" xfId="50"/>
-    <cellStyle name="好" xfId="51"/>
-    <cellStyle name="差" xfId="52"/>
-    <cellStyle name="适中" xfId="53"/>
-    <cellStyle name="强调文字颜色 1" xfId="54"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="55"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="56"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="57"/>
-    <cellStyle name="强调文字颜色 2" xfId="58"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="59"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="60"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="61"/>
-    <cellStyle name="强调文字颜色 3" xfId="62"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="63"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="64"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="65"/>
-    <cellStyle name="强调文字颜色 4" xfId="66"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="67"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="68"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="69"/>
-    <cellStyle name="强调文字颜色 5" xfId="70"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="71"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="72"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="73"/>
-    <cellStyle name="强调文字颜色 6" xfId="74"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="75"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="76"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="77"/>
-    <cellStyle name="Percent" xfId="78"/>
-    <cellStyle name="Currency" xfId="79"/>
-    <cellStyle name="Currency [0]" xfId="80"/>
-    <cellStyle name="Comma" xfId="81"/>
-    <cellStyle name="Comma [0]" xfId="82"/>
+    <cellStyle name="Percent" xfId="30"/>
+    <cellStyle name="Currency" xfId="31"/>
+    <cellStyle name="Currency [0]" xfId="32"/>
+    <cellStyle name="Comma" xfId="33"/>
+    <cellStyle name="Comma [0]" xfId="34"/>
+    <cellStyle name="千位分隔" xfId="35"/>
+    <cellStyle name="货币" xfId="36"/>
+    <cellStyle name="百分比" xfId="37"/>
+    <cellStyle name="千位分隔[0]" xfId="38"/>
+    <cellStyle name="货币[0]" xfId="39"/>
+    <cellStyle name="超链接" xfId="40"/>
+    <cellStyle name="已访问的超链接" xfId="41"/>
+    <cellStyle name="注释" xfId="42"/>
+    <cellStyle name="警告文本" xfId="43"/>
+    <cellStyle name="标题" xfId="44"/>
+    <cellStyle name="解释性文本" xfId="45"/>
+    <cellStyle name="标题 1" xfId="46"/>
+    <cellStyle name="标题 2" xfId="47"/>
+    <cellStyle name="标题 3" xfId="48"/>
+    <cellStyle name="标题 4" xfId="49"/>
+    <cellStyle name="输入" xfId="50"/>
+    <cellStyle name="输出" xfId="51"/>
+    <cellStyle name="计算" xfId="52"/>
+    <cellStyle name="检查单元格" xfId="53"/>
+    <cellStyle name="链接单元格" xfId="54"/>
+    <cellStyle name="汇总" xfId="55"/>
+    <cellStyle name="好" xfId="56"/>
+    <cellStyle name="差" xfId="57"/>
+    <cellStyle name="适中" xfId="58"/>
+    <cellStyle name="强调文字颜色 1" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="60"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="61"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="62"/>
+    <cellStyle name="强调文字颜色 2" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="64"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="65"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="66"/>
+    <cellStyle name="强调文字颜色 3" xfId="67"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="69"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="70"/>
+    <cellStyle name="强调文字颜色 4" xfId="71"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="72"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="73"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="74"/>
+    <cellStyle name="强调文字颜色 5" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="77"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="78"/>
+    <cellStyle name="强调文字颜色 6" xfId="79"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="81"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="82"/>
+    <cellStyle name="Percent" xfId="83"/>
+    <cellStyle name="Currency" xfId="84"/>
+    <cellStyle name="Currency [0]" xfId="85"/>
+    <cellStyle name="Comma" xfId="86"/>
+    <cellStyle name="Comma [0]" xfId="87"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>

--- a/4.质量管理/2.运行记录类文件/TXHS-04-20-2025年度质量指标完成情况.xlsx
+++ b/4.质量管理/2.运行记录类文件/TXHS-04-20-2025年度质量指标完成情况.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="22188" windowHeight="9575" activeTab="0"/>
+    <workbookView windowWidth="22188" windowHeight="9575"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_GoBack" localSheetId="0">#REF!</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -82,7 +82,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>0</t>
@@ -92,7 +91,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>次</t>
@@ -113,7 +111,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -123,7 +120,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>次</t>
@@ -333,7 +329,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>15</t>
@@ -343,7 +338,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>条</t>
@@ -373,7 +367,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -383,7 +376,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>次</t>
@@ -395,7 +387,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -405,7 +396,6 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>次</t>
@@ -440,77 +430,70 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="楷体_GB2312"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF0F1115"/>
       <name val="Consolas"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -518,7 +501,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -527,7 +509,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -536,7 +517,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -545,7 +525,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -554,7 +533,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -563,7 +541,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -571,7 +548,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -580,7 +556,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -589,7 +564,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -598,7 +572,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -606,7 +579,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -615,7 +587,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -623,7 +594,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -631,7 +601,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -639,7 +608,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -647,24 +615,39 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -852,18 +835,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -871,6 +842,47 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -886,6 +898,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -894,6 +907,7 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -902,6 +916,7 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -916,6 +931,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -930,6 +946,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -944,6 +961,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -952,6 +970,7 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -962,446 +981,193 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="88">
+  <cellStyleXfs count="55">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="2" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="1" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="2" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="1" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="74">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
-    <cellStyle name="Percent" xfId="20"/>
-    <cellStyle name="Currency" xfId="21"/>
-    <cellStyle name="Currency [0]" xfId="22"/>
-    <cellStyle name="Comma" xfId="23"/>
-    <cellStyle name="Comma [0]" xfId="24"/>
-    <cellStyle name="Percent" xfId="25"/>
-    <cellStyle name="Currency" xfId="26"/>
-    <cellStyle name="Currency [0]" xfId="27"/>
-    <cellStyle name="Comma" xfId="28"/>
-    <cellStyle name="Comma [0]" xfId="29"/>
-    <cellStyle name="Percent" xfId="30"/>
-    <cellStyle name="Currency" xfId="31"/>
-    <cellStyle name="Currency [0]" xfId="32"/>
-    <cellStyle name="Comma" xfId="33"/>
-    <cellStyle name="Comma [0]" xfId="34"/>
-    <cellStyle name="千位分隔" xfId="35"/>
-    <cellStyle name="货币" xfId="36"/>
-    <cellStyle name="百分比" xfId="37"/>
-    <cellStyle name="千位分隔[0]" xfId="38"/>
-    <cellStyle name="货币[0]" xfId="39"/>
-    <cellStyle name="超链接" xfId="40"/>
-    <cellStyle name="已访问的超链接" xfId="41"/>
-    <cellStyle name="注释" xfId="42"/>
-    <cellStyle name="警告文本" xfId="43"/>
-    <cellStyle name="标题" xfId="44"/>
-    <cellStyle name="解释性文本" xfId="45"/>
-    <cellStyle name="标题 1" xfId="46"/>
-    <cellStyle name="标题 2" xfId="47"/>
-    <cellStyle name="标题 3" xfId="48"/>
-    <cellStyle name="标题 4" xfId="49"/>
-    <cellStyle name="输入" xfId="50"/>
-    <cellStyle name="输出" xfId="51"/>
-    <cellStyle name="计算" xfId="52"/>
-    <cellStyle name="检查单元格" xfId="53"/>
-    <cellStyle name="链接单元格" xfId="54"/>
-    <cellStyle name="汇总" xfId="55"/>
-    <cellStyle name="好" xfId="56"/>
-    <cellStyle name="差" xfId="57"/>
-    <cellStyle name="适中" xfId="58"/>
-    <cellStyle name="强调文字颜色 1" xfId="59"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="60"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="61"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="62"/>
-    <cellStyle name="强调文字颜色 2" xfId="63"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="64"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="65"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="66"/>
-    <cellStyle name="强调文字颜色 3" xfId="67"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="68"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="69"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="70"/>
-    <cellStyle name="强调文字颜色 4" xfId="71"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="72"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="73"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="74"/>
-    <cellStyle name="强调文字颜色 5" xfId="75"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="76"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="77"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="78"/>
-    <cellStyle name="强调文字颜色 6" xfId="79"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="80"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="81"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="82"/>
-    <cellStyle name="Percent" xfId="83"/>
-    <cellStyle name="Currency" xfId="84"/>
-    <cellStyle name="Currency [0]" xfId="85"/>
-    <cellStyle name="Comma" xfId="86"/>
-    <cellStyle name="Comma [0]" xfId="87"/>
+  <cellStyles count="55">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
+    <cellStyle name="Percent" xfId="50"/>
+    <cellStyle name="Currency" xfId="51"/>
+    <cellStyle name="Currency [0]" xfId="52"/>
+    <cellStyle name="Comma" xfId="53"/>
+    <cellStyle name="Comma [0]" xfId="54"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1742,23 +1508,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.62962962962963" style="2" customWidth="1"/>
     <col min="6" max="6" width="6.75" style="2" customWidth="1"/>
-    <col min="7" max="10" width="11.625" style="2" customWidth="1"/>
-    <col min="11" max="15" width="11.625" style="2"/>
-    <col min="16" max="17" width="12.875" style="2"/>
-    <col min="18" max="18" width="12.875" style="1"/>
+    <col min="7" max="10" width="11.6296296296296" style="2" customWidth="1"/>
+    <col min="11" max="15" width="11.6296296296296" style="2"/>
+    <col min="16" max="17" width="12.8796296296296" style="2"/>
+    <col min="18" max="18" width="12.8796296296296" style="1"/>
     <col min="19" max="19" width="9.5" style="1"/>
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="24.75" customHeight="1">
+    <row r="1" ht="24.75" customHeight="1" spans="1:19">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1793,7 +1559,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="24.75" customHeight="1">
+    <row r="2" ht="24.75" customHeight="1" spans="1:19">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1838,7 +1604,7 @@
       </c>
       <c r="S2" s="5"/>
     </row>
-    <row r="3" spans="1:19" ht="14.4">
+    <row r="3" ht="28.8" spans="1:19">
       <c r="A3" s="7">
         <f>ROW()-2</f>
         <v>1</v>
@@ -1890,16 +1656,16 @@
         <v>11</v>
       </c>
       <c r="R3" s="11">
-        <v>0.99399999999999999</v>
+        <v>0.994</v>
       </c>
       <c r="S3" s="10">
         <f>SUM(R3+L3)/2</f>
-        <v>0.98199999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="14.4">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" s="7">
-        <f t="shared" si="0" ref="A4:A13">ROW()-2</f>
+        <f t="shared" ref="A4:A13" si="0">ROW()-2</f>
         <v>2</v>
       </c>
       <c r="B4" s="8"/>
@@ -1953,7 +1719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="14.4">
+    <row r="5" spans="1:19">
       <c r="A5" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2009,7 +1775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="14.4">
+    <row r="6" spans="1:19">
       <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2065,7 +1831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="14.4">
+    <row r="7" spans="1:19">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2123,10 +1889,10 @@
       </c>
       <c r="S7" s="13">
         <f t="array" ref="S7">SUMPRODUCT(--(0&amp;SUBSTITUTE(G7:R7,"-","0")))/IF(F7="季度",4,IF(F7="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2182,10 +1948,10 @@
       </c>
       <c r="S8" s="13">
         <f t="array" ref="S8">SUMPRODUCT(--(0&amp;SUBSTITUTE(G8:R8,"-","0")))/IF(F8="季度",4,IF(F8="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2241,10 +2007,10 @@
       </c>
       <c r="S9" s="13">
         <f t="array" ref="S9">SUMPRODUCT(--(0&amp;SUBSTITUTE(G9:R9,"-","0")))/IF(F9="季度",4,IF(F9="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2300,10 +2066,10 @@
       </c>
       <c r="S10" s="13">
         <f t="array" ref="S10">SUMPRODUCT(--(0&amp;SUBSTITUTE(G10:R10,"-","0")))/IF(F10="季度",4,IF(F10="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2359,10 +2125,10 @@
       </c>
       <c r="S11" s="13">
         <f t="array" ref="S11">SUMPRODUCT(--(0&amp;SUBSTITUTE(G11:R11,"-","0")))/IF(F11="季度",4,IF(F11="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2418,10 +2184,10 @@
       </c>
       <c r="S12" s="13">
         <f t="array" ref="S12">SUMPRODUCT(--(0&amp;SUBSTITUTE(G12:R12,"-","0")))/IF(F12="季度",4,IF(F12="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2481,9 +2247,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.4">
+    <row r="14" spans="1:19">
       <c r="A14" s="7">
-        <f t="shared" si="1" ref="A14:A23">ROW()-2</f>
+        <f t="shared" ref="A14:A23" si="1">ROW()-2</f>
         <v>12</v>
       </c>
       <c r="B14" s="8"/>
@@ -2537,10 +2303,10 @@
       </c>
       <c r="S14" s="13">
         <f t="array" ref="S14">SUMPRODUCT(--(0&amp;SUBSTITUTE(G14:R14,"-","0")))/IF(F14="季度",4,IF(F14="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="7">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -2596,10 +2362,10 @@
       </c>
       <c r="S15" s="13">
         <f t="array" ref="S15">SUMPRODUCT(--(0&amp;SUBSTITUTE(G15:R15,"-","0")))/IF(F15="季度",4,IF(F15="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="7">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2655,10 +2421,10 @@
       </c>
       <c r="S16" s="13">
         <f t="array" ref="S16">SUMPRODUCT(--(0&amp;SUBSTITUTE(G16:R16,"-","0")))/IF(F16="季度",4,IF(F16="月度",12,1))</f>
-        <v>0.083333333333333329</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="7">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2712,10 +2478,10 @@
       </c>
       <c r="S17" s="13">
         <f t="array" ref="S17">SUMPRODUCT(--(0&amp;SUBSTITUTE(G17:R17,"-","0")))/IF(F17="季度",4,IF(F17="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="7">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -2740,7 +2506,7 @@
         <v>11</v>
       </c>
       <c r="I18" s="10">
-        <v>0.90</v>
+        <v>0.9</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>11</v>
@@ -2771,10 +2537,10 @@
       </c>
       <c r="S18" s="13">
         <f t="array" ref="S18">SUMPRODUCT(--(0&amp;SUBSTITUTE(G18:R18,"-","0")))/IF(F18="季度",4,IF(F18="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="14.4">
+        <v>0.955</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="7">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -2828,10 +2594,10 @@
       </c>
       <c r="S19" s="13">
         <f t="array" ref="S19">SUMPRODUCT(--(0&amp;SUBSTITUTE(G19:R19,"-","0")))/IF(F19="季度",4,IF(F19="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="14.4">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -2889,7 +2655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="14.4">
+    <row r="21" spans="1:19">
       <c r="A21" s="7">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -2945,10 +2711,10 @@
       </c>
       <c r="S21" s="13">
         <f t="array" ref="S21">SUMPRODUCT(--(0&amp;SUBSTITUTE(G21:R21,"-","0")))/IF(F21="季度",4,IF(F21="月度",12,1))</f>
-        <v>0.081666666666666665</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="14.4">
+        <v>0.990833333333333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="7">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -3004,10 +2770,10 @@
       </c>
       <c r="S22" s="13">
         <f t="array" ref="S22">SUMPRODUCT(--(0&amp;SUBSTITUTE(G22:R22,"-","0")))/IF(F22="季度",4,IF(F22="月度",12,1))</f>
-        <v>0.083333333333333329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="7">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -3063,12 +2829,12 @@
       </c>
       <c r="S23" s="13">
         <f t="array" ref="S23">SUMPRODUCT(--(0&amp;SUBSTITUTE(G23:R23,"-","0")))/IF(F23="季度",4,IF(F23="月度",12,1))</f>
-        <v>0.083333333333333329</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="7">
-        <f t="shared" si="2" ref="A24:A35">ROW()-2</f>
+        <f t="shared" ref="A24:A35" si="2">ROW()-2</f>
         <v>22</v>
       </c>
       <c r="B24" s="8"/>
@@ -3122,7 +2888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="14.4">
+    <row r="25" spans="1:19">
       <c r="A25" s="7">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -3180,7 +2946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="14.4">
+    <row r="26" spans="1:19">
       <c r="A26" s="7">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -3238,7 +3004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="14.4">
+    <row r="27" spans="1:19">
       <c r="A27" s="7">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -3294,10 +3060,10 @@
       </c>
       <c r="S27" s="13">
         <f t="array" ref="S27">SUMPRODUCT(--(0&amp;SUBSTITUTE(G27:R27,"-","0")))/IF(F27="季度",4,IF(F27="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="7">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -3351,10 +3117,10 @@
       </c>
       <c r="S28" s="13">
         <f t="array" ref="S28">SUMPRODUCT(--(0&amp;SUBSTITUTE(G28:R28,"-","0")))/IF(F28="季度",4,IF(F28="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="7">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -3412,10 +3178,10 @@
       </c>
       <c r="S29" s="13">
         <f t="array" ref="S29">SUMPRODUCT(--(0&amp;SUBSTITUTE(G29:R29,"-","0")))/IF(F29="季度",4,IF(F29="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="7">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -3440,7 +3206,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="10">
-        <v>0.90</v>
+        <v>0.9</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>11</v>
@@ -3471,10 +3237,10 @@
       </c>
       <c r="S30" s="13">
         <f t="array" ref="S30">SUMPRODUCT(--(0&amp;SUBSTITUTE(G30:R30,"-","0")))/IF(F30="季度",4,IF(F30="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="14.4">
+        <v>0.9425</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="7"/>
       <c r="B31" s="8"/>
       <c r="C31" s="16" t="s">
@@ -3529,7 +3295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="14.4">
+    <row r="32" spans="1:19">
       <c r="A32" s="7"/>
       <c r="B32" s="8"/>
       <c r="C32" s="17"/>
@@ -3580,10 +3346,10 @@
       </c>
       <c r="S32" s="13">
         <f t="array" ref="S32">SUMPRODUCT(--(0&amp;SUBSTITUTE(G32:R32,"-","0")))/IF(F32="季度",4,IF(F32="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="7">
         <f>ROW()-2</f>
         <v>31</v>
@@ -3641,7 +3407,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="16" customHeight="1">
+    <row r="34" ht="16" customHeight="1" spans="1:19">
       <c r="A34" s="7">
         <f>ROW()-2</f>
         <v>32</v>
@@ -3699,7 +3465,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="14.4">
+    <row r="35" spans="1:19">
       <c r="A35" s="7">
         <f>ROW()-2</f>
         <v>33</v>
@@ -3757,7 +3523,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="14.4">
+    <row r="36" spans="1:19">
       <c r="A36" s="7">
         <f>ROW()-2</f>
         <v>34</v>
@@ -3813,10 +3579,10 @@
       </c>
       <c r="S36" s="13">
         <f t="array" ref="S36">SUMPRODUCT(--(0&amp;SUBSTITUTE(G36:R36,"-","0")))/IF(F36="季度",4,IF(F36="月度",12,1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="14.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" s="7">
         <f>ROW()-2</f>
         <v>35</v>
@@ -3874,7 +3640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="71" customHeight="1">
+    <row r="38" ht="71" customHeight="1" spans="1:19">
       <c r="A38" s="20" t="s">
         <v>99</v>
       </c>
@@ -3920,7 +3686,7 @@
     <mergeCell ref="B27:C28"/>
   </mergeCells>
   <pageMargins left="0.707638888888889" right="0.511805555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9" scale="10"/>
+  <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>